--- a/artfynd/A 29844-2025 artfynd.xlsx
+++ b/artfynd/A 29844-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130226240</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>130226227</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130226182</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29844-2025 artfynd.xlsx
+++ b/artfynd/A 29844-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>130226227</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130226182</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29844-2025 artfynd.xlsx
+++ b/artfynd/A 29844-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130226240</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>130226227</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130226182</v>
       </c>
       <c r="B5" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29844-2025 artfynd.xlsx
+++ b/artfynd/A 29844-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130226240</v>
       </c>
       <c r="B3" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>130226227</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>130226182</v>
       </c>
       <c r="B5" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
